--- a/data/trans_dic/P36$fruta-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P36$fruta-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, fruta o zumo</t>
+          <t>Población que desayuna, al menos, fruta o zumo (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,36</t>
+          <t>1,55; 4,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,34; 10,8</t>
+          <t>6,38; 10,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,31; 15,36</t>
+          <t>10,31; 15,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,99; 7,31</t>
+          <t>4,04; 7,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,36; 13,07</t>
+          <t>8,46; 13,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,04; 14,92</t>
+          <t>9,98; 15,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 5,16</t>
+          <t>3,17; 5,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,02; 11,28</t>
+          <t>7,94; 10,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,74; 14,33</t>
+          <t>10,85; 14,54</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,9; 10,74</t>
+          <t>7,02; 10,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,16; 11,77</t>
+          <t>8,16; 11,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,44; 15,75</t>
+          <t>11,16; 15,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,49; 13,72</t>
+          <t>9,55; 13,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,49; 12,44</t>
+          <t>8,39; 12,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,69; 15,86</t>
+          <t>11,67; 16,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,78; 11,73</t>
+          <t>8,72; 11,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,8; 11,57</t>
+          <t>8,83; 11,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,16; 15,37</t>
+          <t>12,09; 15,46</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,46; 13,66</t>
+          <t>8,5; 13,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,96; 18,83</t>
+          <t>12,82; 18,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,67; 14,89</t>
+          <t>9,39; 14,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,92; 17,17</t>
+          <t>11,69; 17,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,5; 17,82</t>
+          <t>12,28; 17,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,15; 17,29</t>
+          <t>12,27; 17,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,79; 14,42</t>
+          <t>10,95; 14,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,44; 17,58</t>
+          <t>13,19; 17,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,73; 15,23</t>
+          <t>11,83; 15,24</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,14; 11,92</t>
+          <t>8,03; 11,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,89; 16,36</t>
+          <t>12,02; 16,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,29; 15,81</t>
+          <t>11,24; 15,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,0; 12,66</t>
+          <t>8,82; 12,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,45; 16,84</t>
+          <t>12,09; 16,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,52; 14,88</t>
+          <t>10,47; 15,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,0; 11,74</t>
+          <t>9,01; 11,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,81; 15,9</t>
+          <t>12,78; 16,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,27; 14,39</t>
+          <t>11,42; 14,42</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,17; 9,19</t>
+          <t>7,11; 9,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,97; 13,25</t>
+          <t>10,89; 13,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,9; 14,16</t>
+          <t>11,88; 14,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,66; 11,82</t>
+          <t>9,54; 11,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,53; 13,74</t>
+          <t>11,57; 13,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,31; 14,69</t>
+          <t>12,17; 14,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,72; 10,18</t>
+          <t>8,63; 10,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,46; 13,09</t>
+          <t>11,44; 13,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,34; 14,01</t>
+          <t>12,34; 13,99</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, fruta o zumo</t>
+          <t>Población que desayuna, al menos, fruta o zumo (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10653; 30232</t>
+          <t>10735; 29699</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>44445; 75728</t>
+          <t>44787; 74909</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>69397; 103350</t>
+          <t>69388; 102612</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27474; 50310</t>
+          <t>27801; 51981</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>58210; 90981</t>
+          <t>58858; 91808</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>67408; 100180</t>
+          <t>67061; 102862</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43604; 71303</t>
+          <t>43786; 72174</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>112062; 157647</t>
+          <t>110986; 153645</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>144370; 192649</t>
+          <t>145922; 195474</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>66148; 102965</t>
+          <t>67353; 103612</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>83107; 119788</t>
+          <t>83044; 121743</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>116872; 160819</t>
+          <t>113991; 161631</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>91796; 132733</t>
+          <t>92410; 132428</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>87447; 128115</t>
+          <t>86379; 128591</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>121782; 165278</t>
+          <t>121558; 166886</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>169172; 225859</t>
+          <t>168061; 223944</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>180147; 237027</t>
+          <t>180758; 235672</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>250816; 317118</t>
+          <t>249408; 319058</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>57303; 92527</t>
+          <t>57568; 90825</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>97914; 142293</t>
+          <t>96837; 142775</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>73318; 112916</t>
+          <t>71247; 111777</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>81498; 117405</t>
+          <t>79923; 117206</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>96987; 138321</t>
+          <t>95313; 138063</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>95409; 135743</t>
+          <t>96348; 136807</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>146882; 196360</t>
+          <t>149100; 196562</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>205886; 269355</t>
+          <t>202070; 263561</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>181116; 235079</t>
+          <t>182551; 235301</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>76534; 112127</t>
+          <t>75555; 109832</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>112431; 154744</t>
+          <t>113694; 154605</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>105843; 148259</t>
+          <t>105407; 147609</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>93241; 131121</t>
+          <t>91388; 133481</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>130680; 176752</t>
+          <t>126964; 175607</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>109669; 155167</t>
+          <t>109145; 156504</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>177850; 231897</t>
+          <t>178094; 231591</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>255672; 317317</t>
+          <t>255007; 319288</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>223228; 284938</t>
+          <t>226136; 285557</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>234573; 300452</t>
+          <t>232577; 300228</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>375159; 453293</t>
+          <t>372498; 451700</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>403547; 479964</t>
+          <t>402872; 485161</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>326152; 398925</t>
+          <t>321891; 392999</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>409578; 488101</t>
+          <t>411155; 490463</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>435813; 520047</t>
+          <t>431133; 512593</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>579619; 676510</t>
+          <t>573255; 671909</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>798805; 912944</t>
+          <t>797553; 915117</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>855413; 971375</t>
+          <t>855408; 969735</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36$fruta-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P36$fruta-Habitat-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,29</t>
+          <t>1,59; 4,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,38; 10,68</t>
+          <t>6,48; 10,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,31; 15,25</t>
+          <t>9,99; 15,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,04; 7,55</t>
+          <t>4,11; 7,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,46; 13,19</t>
+          <t>8,27; 13,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,98; 15,31</t>
+          <t>10,14; 15,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,17; 5,22</t>
+          <t>3,18; 5,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,94; 10,99</t>
+          <t>7,82; 11,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,85; 14,54</t>
+          <t>10,92; 14,46</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,02; 10,81</t>
+          <t>6,89; 10,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,16; 11,96</t>
+          <t>8,03; 11,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,16; 15,83</t>
+          <t>11,26; 15,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,55; 13,69</t>
+          <t>9,59; 13,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,39; 12,48</t>
+          <t>8,38; 12,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,67; 16,02</t>
+          <t>11,62; 16,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,72; 11,63</t>
+          <t>8,8; 11,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,83; 11,51</t>
+          <t>8,78; 11,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,09; 15,46</t>
+          <t>12,21; 15,24</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,5; 13,41</t>
+          <t>8,32; 13,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,82; 18,9</t>
+          <t>12,93; 18,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,39; 14,74</t>
+          <t>9,92; 15,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,69; 17,14</t>
+          <t>11,87; 17,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,28; 17,79</t>
+          <t>12,56; 17,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,27; 17,43</t>
+          <t>12,19; 17,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,95; 14,44</t>
+          <t>10,81; 14,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,19; 17,21</t>
+          <t>13,3; 17,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,83; 15,24</t>
+          <t>11,82; 15,39</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,03; 11,68</t>
+          <t>8,05; 11,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,02; 16,35</t>
+          <t>11,92; 16,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,24; 15,74</t>
+          <t>11,25; 15,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,82; 12,89</t>
+          <t>8,8; 12,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,09; 16,73</t>
+          <t>12,31; 16,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,47; 15,01</t>
+          <t>10,31; 14,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,01; 11,72</t>
+          <t>8,95; 11,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,78; 16,0</t>
+          <t>12,92; 15,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,42; 14,42</t>
+          <t>11,36; 14,53</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,11; 9,18</t>
+          <t>7,12; 9,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,89; 13,2</t>
+          <t>10,93; 13,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,88; 14,31</t>
+          <t>11,97; 14,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,54; 11,64</t>
+          <t>9,69; 11,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,57; 13,81</t>
+          <t>11,47; 13,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,17; 14,47</t>
+          <t>12,2; 14,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,63; 10,11</t>
+          <t>8,66; 10,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,44; 13,12</t>
+          <t>11,48; 13,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,34; 13,99</t>
+          <t>12,37; 14,0</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10735; 29699</t>
+          <t>11044; 29272</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>44787; 74909</t>
+          <t>45441; 74824</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>69388; 102612</t>
+          <t>67219; 102217</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27801; 51981</t>
+          <t>28282; 51327</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>58858; 91808</t>
+          <t>57577; 93404</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>67061; 102862</t>
+          <t>68134; 101979</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43786; 72174</t>
+          <t>43968; 71623</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>110986; 153645</t>
+          <t>109323; 155581</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>145922; 195474</t>
+          <t>146898; 194401</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>67353; 103612</t>
+          <t>66042; 103302</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>83044; 121743</t>
+          <t>81729; 121592</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>113991; 161631</t>
+          <t>115049; 161237</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>92410; 132428</t>
+          <t>92817; 135085</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>86379; 128591</t>
+          <t>86327; 129502</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>121558; 166886</t>
+          <t>121043; 169323</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>168061; 223944</t>
+          <t>169567; 225471</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>180758; 235672</t>
+          <t>179777; 237995</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>249408; 319058</t>
+          <t>251917; 314467</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>57568; 90825</t>
+          <t>56336; 89502</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>96837; 142775</t>
+          <t>97683; 142387</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>71247; 111777</t>
+          <t>75252; 113985</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>79923; 117206</t>
+          <t>81180; 116433</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>95313; 138063</t>
+          <t>97452; 138769</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>96348; 136807</t>
+          <t>95713; 135413</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>149100; 196562</t>
+          <t>147119; 199069</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>202070; 263561</t>
+          <t>203724; 261635</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>182551; 235301</t>
+          <t>182378; 237595</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>75555; 109832</t>
+          <t>75721; 112462</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>113694; 154605</t>
+          <t>112762; 155543</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>105407; 147609</t>
+          <t>105469; 148921</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>91388; 133481</t>
+          <t>91093; 131671</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>126964; 175607</t>
+          <t>129253; 172921</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>109145; 156504</t>
+          <t>107520; 153038</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>178094; 231591</t>
+          <t>176867; 230318</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>255007; 319288</t>
+          <t>257821; 319182</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>226136; 285557</t>
+          <t>225027; 287758</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>232577; 300228</t>
+          <t>232687; 298110</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>372498; 451700</t>
+          <t>373824; 450597</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>402872; 485161</t>
+          <t>405948; 481800</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>321891; 392999</t>
+          <t>327110; 401198</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>411155; 490463</t>
+          <t>407260; 490212</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>431133; 512593</t>
+          <t>432130; 512662</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>573255; 671909</t>
+          <t>575757; 672395</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>797553; 915117</t>
+          <t>800775; 916990</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>855408; 969735</t>
+          <t>857136; 970154</t>
         </is>
       </c>
     </row>
